--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260713.xlsx
@@ -711,17 +711,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7,064,000</t>
+          <t>7,800,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7,800,000</t>
+          <t>7,064,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
